--- a/AI_MOLE/Test_Bench/Pneumatic_Cylinder/Experiment_log.xlsx
+++ b/AI_MOLE/Test_Bench/Pneumatic_Cylinder/Experiment_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programmierung_Ole\Masterarbeit_AI_MOLE\AI_MOLE\Test_Bench\Pneumatic_Cylinder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77523D0-22FB-4857-B352-368F821A85D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF656850-534D-432D-9B46-66D7645AD48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Versuchsprotokoll (MOLE)" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="55">
   <si>
     <t>Datum</t>
   </si>
@@ -185,6 +188,12 @@
   </si>
   <si>
     <t>ja</t>
+  </si>
+  <si>
+    <t>Trajektorie an Prüfstand angepasst, jedoch schlechte Initialisierung</t>
+  </si>
+  <si>
+    <t>Trajektorie an Prüfstand angepasst, bessere Initialisierung</t>
   </si>
 </sst>
 </file>
@@ -669,23 +678,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="23" style="2" customWidth="1"/>
     <col min="7" max="7" width="22" style="2" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="16.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18.7109375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="18.42578125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="30.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="18.44140625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="30.109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -723,7 +732,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>46084</v>
       </c>
@@ -761,7 +770,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>46084</v>
       </c>
@@ -799,7 +808,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>46084</v>
       </c>
@@ -837,7 +846,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>46084</v>
       </c>
@@ -875,7 +884,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>46085</v>
       </c>
@@ -913,7 +922,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>46085</v>
       </c>
@@ -951,7 +960,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>46085</v>
       </c>
@@ -989,7 +998,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>46085</v>
       </c>
@@ -1027,7 +1036,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>46085</v>
       </c>
@@ -1059,7 +1068,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>46085</v>
       </c>
@@ -1091,7 +1100,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>46085</v>
       </c>
@@ -1129,82 +1138,82 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="C13" s="6"/>
       <c r="L13" s="6"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="C14" s="6"/>
       <c r="L14" s="6"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="C15" s="6"/>
       <c r="L15" s="6"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="C16" s="6"/>
       <c r="L16" s="6"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="C17" s="6"/>
       <c r="L17" s="6"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="C18" s="6"/>
       <c r="L18" s="6"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="C19" s="6"/>
       <c r="L19" s="6"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="C20" s="6"/>
       <c r="L20" s="6"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="C21" s="6"/>
       <c r="L21" s="6"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="C22" s="6"/>
       <c r="L22" s="6"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="C23" s="6"/>
       <c r="L23" s="6"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="C24" s="6"/>
       <c r="L24" s="6"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="C25" s="6"/>
       <c r="L25" s="6"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="C26" s="6"/>
       <c r="L26" s="6"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="C27" s="6"/>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="C28" s="6"/>
       <c r="L28" s="6"/>
@@ -1221,18 +1230,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9381838-4D60-4571-ADD6-94E4FB4B0EC8}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="2"/>
-    <col min="4" max="4" width="22.5703125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="23.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="2"/>
+    <col min="4" max="4" width="22.5546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -1255,7 +1264,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -1263,13 +1272,13 @@
         <v>0.01</v>
       </c>
       <c r="C2" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="2">
-        <v>5.5</v>
+        <v>0.3</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>26</v>
@@ -1278,7 +1287,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -1286,42 +1295,42 @@
         <v>0.01</v>
       </c>
       <c r="C3" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E3" s="2">
-        <v>24.4</v>
+        <v>0.33700000000000002</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B4" s="2">
         <v>0.05</v>
       </c>
       <c r="C4" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E4" s="2">
-        <v>24.4</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/AI_MOLE/Test_Bench/Pneumatic_Cylinder/Experiment_log.xlsx
+++ b/AI_MOLE/Test_Bench/Pneumatic_Cylinder/Experiment_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programmierung_Ole\Masterarbeit_AI_MOLE\AI_MOLE\Test_Bench\Pneumatic_Cylinder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF656850-534D-432D-9B46-66D7645AD48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58FF1E5-B41C-4ACA-8172-F2485165DC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Versuchsprotokoll (MOLE)" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="58">
   <si>
     <t>Datum</t>
   </si>
@@ -194,6 +194,15 @@
   </si>
   <si>
     <t>Trajektorie an Prüfstand angepasst, bessere Initialisierung</t>
+  </si>
+  <si>
+    <t>Trajectory_04</t>
+  </si>
+  <si>
+    <t>Schnelle Trajektorie an Prüfstand angepasst, bessere Initialisierung</t>
+  </si>
+  <si>
+    <t>Weiterer Run mit dem stochastic Ansatz, jedoch mit einer schnelleren Trajektorie</t>
   </si>
 </sst>
 </file>
@@ -378,8 +387,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{64AE17CE-7A85-4552-B08B-1317F901654A}" name="Tabelle1" displayName="Tabelle1" ref="A1:L12" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
-  <autoFilter ref="A1:L12" xr:uid="{64AE17CE-7A85-4552-B08B-1317F901654A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{64AE17CE-7A85-4552-B08B-1317F901654A}" name="Tabelle1" displayName="Tabelle1" ref="A1:L13" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+  <autoFilter ref="A1:L13" xr:uid="{64AE17CE-7A85-4552-B08B-1317F901654A}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{57E8A950-5641-4CEF-96CF-9E419B47D19C}" name="Datum" dataDxfId="20"/>
     <tableColumn id="2" xr3:uid="{91C5A9D0-5D8D-4481-8037-952760167E31}" name="Dateiname" dataDxfId="19"/>
@@ -399,8 +408,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{43DA8F1D-6502-4878-8009-693EAB99A35A}" name="Tabelle2" displayName="Tabelle2" ref="A1:G4" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G4" xr:uid="{43DA8F1D-6502-4878-8009-693EAB99A35A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{43DA8F1D-6502-4878-8009-693EAB99A35A}" name="Tabelle2" displayName="Tabelle2" ref="A1:G5" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G5" xr:uid="{43DA8F1D-6502-4878-8009-693EAB99A35A}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{1FA48B55-6A3F-4007-B441-9696E9D798AA}" name="Dateiname" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{EDF3DA31-D44E-4CB4-A1F9-F4CABAFCB2AD}" name="Abtastzeit Ts [s]" dataDxfId="5"/>
@@ -1138,10 +1147,43 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="C13" s="6"/>
-      <c r="L13" s="6"/>
+    <row r="13" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>46086</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="2">
+        <v>20</v>
+      </c>
+      <c r="F13" s="2">
+        <v>3</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
@@ -1229,7 +1271,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9381838-4D60-4571-ADD6-94E4FB4B0EC8}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="2" customWidth="1"/>
@@ -1333,6 +1375,29 @@
         <v>54</v>
       </c>
     </row>
+    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.31850000000000001</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <tableParts count="1">
